--- a/vocafile/Hackers_Voca_Day2_with_Synonyms.xlsx
+++ b/vocafile/Hackers_Voca_Day2_with_Synonyms.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태범\Desktop\해커스보카\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A502D001-8887-48D1-90D4-396706FAD60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="192">
   <si>
     <t>번호</t>
   </si>
@@ -595,12 +601,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -608,8 +614,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -655,17 +668,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -703,7 +724,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -737,6 +758,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -771,9 +793,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -946,11 +969,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,7 +990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -984,7 +1007,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1001,7 +1024,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1018,7 +1041,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1035,7 +1058,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1052,7 +1075,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1069,7 +1092,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
@@ -1080,7 +1109,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" t="s">
         <v>64</v>
       </c>
@@ -1091,7 +1126,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1108,7 +1143,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
       <c r="C11" t="s">
         <v>62</v>
       </c>
@@ -1119,7 +1160,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1136,7 +1177,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1153,7 +1194,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1170,7 +1211,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1187,7 +1228,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1204,7 +1245,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1221,7 +1262,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>14</v>
       </c>
@@ -1238,7 +1279,13 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
       <c r="C19" t="s">
         <v>64</v>
       </c>
@@ -1249,7 +1296,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1266,7 +1313,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1283,7 +1330,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1300,7 +1347,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1317,7 +1364,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1334,7 +1381,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>20</v>
       </c>
@@ -1351,7 +1398,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1368,7 +1415,13 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
       <c r="C27" t="s">
         <v>65</v>
       </c>
@@ -1379,7 +1432,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>22</v>
       </c>
@@ -1396,7 +1449,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>23</v>
       </c>
@@ -1413,7 +1466,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>24</v>
       </c>
@@ -1430,7 +1483,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>25</v>
       </c>
@@ -1447,7 +1500,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>26</v>
       </c>
@@ -1464,7 +1517,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>27</v>
       </c>
@@ -1481,7 +1534,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>28</v>
       </c>
@@ -1498,7 +1551,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>29</v>
       </c>
@@ -1515,7 +1568,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>30</v>
       </c>
@@ -1532,7 +1585,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>31</v>
       </c>
@@ -1549,7 +1602,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>32</v>
       </c>
@@ -1566,7 +1619,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>33</v>
       </c>
@@ -1583,7 +1636,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>34</v>
       </c>
@@ -1600,7 +1653,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>35</v>
       </c>
@@ -1617,7 +1670,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>36</v>
       </c>
@@ -1634,7 +1687,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>37</v>
       </c>
@@ -1651,7 +1704,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>38</v>
       </c>
@@ -1668,7 +1721,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>39</v>
       </c>
@@ -1685,7 +1738,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>43</v>
+      </c>
       <c r="C46" t="s">
         <v>64</v>
       </c>
@@ -1696,7 +1755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>40</v>
       </c>
@@ -1713,7 +1772,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>41</v>
       </c>
@@ -1730,7 +1789,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>42</v>
       </c>
@@ -1747,7 +1806,13 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
       <c r="C50" t="s">
         <v>64</v>
       </c>
@@ -1758,7 +1823,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>43</v>
       </c>
@@ -1775,7 +1840,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>44</v>
       </c>
@@ -1792,7 +1857,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>45</v>
       </c>
@@ -1809,7 +1874,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>46</v>
       </c>
@@ -1826,7 +1891,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>47</v>
       </c>
@@ -1843,7 +1908,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>48</v>
       </c>
@@ -1860,7 +1925,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>49</v>
       </c>
@@ -1877,7 +1942,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>50</v>
       </c>
@@ -1894,7 +1959,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>51</v>
       </c>
@@ -1911,7 +1976,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>52</v>
       </c>
@@ -1928,7 +1993,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>53</v>
       </c>
@@ -1945,7 +2010,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>54</v>
       </c>
@@ -1962,7 +2027,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>55</v>
       </c>
@@ -1979,7 +2044,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>56</v>
       </c>
@@ -1997,6 +2062,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>